--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/1mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/1mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.62068909722</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>234.3311902789017</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>230.5822789751589</v>
+        <v>0.258798134</v>
+      </c>
+      <c r="Y2">
+        <v>0.263068096</v>
+      </c>
+      <c r="Z2">
+        <v>0.3690275020848001</v>
+      </c>
+      <c r="AA2">
+        <v>2.134980999999996</v>
+      </c>
+      <c r="AB2">
+        <v>0.1731371730258665</v>
+      </c>
+      <c r="AC2">
+        <v>40.57143983667545</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.62080483796</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>232.6101484575447</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>231.388509969266</v>
+      </c>
+      <c r="X3">
+        <v>0.258819136</v>
+      </c>
+      <c r="Y3">
+        <v>0.263070326</v>
+      </c>
+      <c r="Z3">
+        <v>0.3690438206792424</v>
+      </c>
+      <c r="AA3">
+        <v>2.125594999999997</v>
+      </c>
+      <c r="AB3">
+        <v>0.1739068153331388</v>
+      </c>
+      <c r="AC3">
+        <v>40.45249013242022</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.62092115741</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>232.6373313812239</v>
       </c>
-      <c r="V4">
-        <v>0.9858906149130339</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.258828682</v>
+      </c>
+      <c r="Y4">
+        <v>0.26307128</v>
+      </c>
+      <c r="Z4">
+        <v>0.3690511956174855</v>
+      </c>
+      <c r="AA4">
+        <v>2.121299</v>
+      </c>
+      <c r="AB4">
+        <v>0.1742613144694085</v>
+      </c>
+      <c r="AC4">
+        <v>40.53968716114746</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.62103689815</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>232.0657625169484</v>
       </c>
-      <c r="V5">
-        <v>0.3224349883485085</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>40.53585846788042</v>
+      </c>
+      <c r="X5">
+        <v>0.2588255</v>
+      </c>
+      <c r="Y5">
+        <v>0.263080514</v>
+      </c>
+      <c r="Z5">
+        <v>0.3690555463568515</v>
+      </c>
+      <c r="AA5">
+        <v>2.127506999999994</v>
+      </c>
+      <c r="AB5">
+        <v>0.1737565438384938</v>
+      </c>
+      <c r="AC5">
+        <v>40.32294483818963</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.62115263889</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>232.0646752677087</v>
       </c>
-      <c r="V6">
-        <v>0.3303097468201982</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.258851274</v>
+      </c>
+      <c r="Y6">
+        <v>0.263092612</v>
+      </c>
+      <c r="Z6">
+        <v>0.3690822463088758</v>
+      </c>
+      <c r="AA6">
+        <v>2.120668999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.1743275307029326</v>
+      </c>
+      <c r="AC6">
+        <v>40.45526180279756</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.62126895833</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>232.4491389250314</v>
       </c>
-      <c r="V7">
-        <v>0.2216570008622944</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.258865274</v>
+      </c>
+      <c r="Y7">
+        <v>0.263093566</v>
+      </c>
+      <c r="Z7">
+        <v>0.36909274519244</v>
+      </c>
+      <c r="AA7">
+        <v>2.114145999999998</v>
+      </c>
+      <c r="AB7">
+        <v>0.1748685927268929</v>
+      </c>
+      <c r="AC7">
+        <v>40.64805380439826</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.62138469907</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>232.0290190059019</v>
       </c>
-      <c r="V8">
-        <v>0.2329464957372326</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.258872274</v>
+      </c>
+      <c r="Y8">
+        <v>0.263101526</v>
+      </c>
+      <c r="Z8">
+        <v>0.3691033286621238</v>
+      </c>
+      <c r="AA8">
+        <v>2.114626000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.1748340257355801</v>
+      </c>
+      <c r="AC8">
+        <v>40.56656748027925</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.62150101852</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>231.8400599191422</v>
       </c>
-      <c r="V9">
-        <v>0.3117647399171239</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.258880866</v>
+      </c>
+      <c r="Y9">
+        <v>0.263112032</v>
+      </c>
+      <c r="Z9">
+        <v>0.3691168435117517</v>
+      </c>
+      <c r="AA9">
+        <v>2.115583000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.1747615748047895</v>
+      </c>
+      <c r="AC9">
+        <v>40.51673397430605</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.62161675926</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>231.8276744611133</v>
       </c>
-      <c r="V10">
-        <v>0.1128410103906213</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.258885638</v>
+      </c>
+      <c r="Y10">
+        <v>0.263117126</v>
+      </c>
+      <c r="Z10">
+        <v>0.3691238214436545</v>
+      </c>
+      <c r="AA10">
+        <v>2.115743999999999</v>
+      </c>
+      <c r="AB10">
+        <v>0.1747516123579306</v>
+      </c>
+      <c r="AC10">
+        <v>40.51225990126899</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.6217325</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>231.6562993252204</v>
       </c>
-      <c r="V11">
-        <v>0.1027057225373382</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.258889776</v>
+      </c>
+      <c r="Y11">
+        <v>0.26312031</v>
+      </c>
+      <c r="Z11">
+        <v>0.3691289932419645</v>
+      </c>
+      <c r="AA11">
+        <v>2.115267000000003</v>
+      </c>
+      <c r="AB11">
+        <v>0.1747933314025863</v>
+      </c>
+      <c r="AC11">
+        <v>40.49197629944997</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.62184881944</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>231.4370820524728</v>
       </c>
-      <c r="V12">
-        <v>0.1957839283329803</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.25889964</v>
+      </c>
+      <c r="Y12">
+        <v>0.263120628</v>
+      </c>
+      <c r="Z12">
+        <v>0.3691361381269029</v>
+      </c>
+      <c r="AA12">
+        <v>2.110493999999996</v>
+      </c>
+      <c r="AB12">
+        <v>0.1751907237778456</v>
+      </c>
+      <c r="AC12">
+        <v>40.54562991380534</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.62196456019</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>230.7775989752588</v>
       </c>
-      <c r="V13">
-        <v>0.4573635400906564</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.25890473</v>
+      </c>
+      <c r="Y13">
+        <v>0.26312031</v>
+      </c>
+      <c r="Z13">
+        <v>0.3691394814306227</v>
+      </c>
+      <c r="AA13">
+        <v>2.107790000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.1754163207816209</v>
+      </c>
+      <c r="AC13">
+        <v>40.48215733105627</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.62208030093</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>230.8489149475235</v>
       </c>
-      <c r="V14">
-        <v>0.3619264290746969</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.258905686</v>
+      </c>
+      <c r="Y14">
+        <v>0.263120946</v>
+      </c>
+      <c r="Z14">
+        <v>0.3691406052807866</v>
+      </c>
+      <c r="AA14">
+        <v>2.10763</v>
+      </c>
+      <c r="AB14">
+        <v>0.1754301265378478</v>
+      </c>
+      <c r="AC14">
+        <v>40.49785436036891</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.62219604167</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>230.8245322069117</v>
       </c>
-      <c r="V15">
-        <v>0.03624733133551897</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.258921596</v>
+      </c>
+      <c r="Y15">
+        <v>0.263133044</v>
+      </c>
+      <c r="Z15">
+        <v>0.3691603875280948</v>
+      </c>
+      <c r="AA15">
+        <v>2.105724000000002</v>
+      </c>
+      <c r="AB15">
+        <v>0.1755977809787519</v>
+      </c>
+      <c r="AC15">
+        <v>40.53227565099214</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.62231236111</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>230.5633800769529</v>
       </c>
-      <c r="V16">
-        <v>0.1582851410872583</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.258928596</v>
+      </c>
+      <c r="Y16">
+        <v>0.263138776</v>
+      </c>
+      <c r="Z16">
+        <v>0.3691693828871909</v>
+      </c>
+      <c r="AA16">
+        <v>2.105089999999997</v>
+      </c>
+      <c r="AB16">
+        <v>0.1756547613286726</v>
+      </c>
+      <c r="AC16">
+        <v>40.49955549854919</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.62242868056</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>230.9714412346287</v>
       </c>
-      <c r="V17">
-        <v>0.2066787385497467</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.25892796</v>
+      </c>
+      <c r="Y17">
+        <v>0.263127314</v>
+      </c>
+      <c r="Z17">
+        <v>0.3691607669330751</v>
+      </c>
+      <c r="AA17">
+        <v>2.099677</v>
+      </c>
+      <c r="AB17">
+        <v>0.1761020394135314</v>
+      </c>
+      <c r="AC17">
+        <v>40.67454184770074</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.622545</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>231.4901882788506</v>
       </c>
-      <c r="V18">
-        <v>0.4645043680092444</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.258925096</v>
+      </c>
+      <c r="Y18">
+        <v>0.263132726</v>
+      </c>
+      <c r="Z18">
+        <v>0.3691626157004529</v>
+      </c>
+      <c r="AA18">
+        <v>2.103815000000004</v>
+      </c>
+      <c r="AB18">
+        <v>0.1757576591402723</v>
+      </c>
+      <c r="AC18">
+        <v>40.68617360583169</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.62266131944</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>230.2935777305587</v>
       </c>
-      <c r="V19">
-        <v>0.6000658617078528</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.258923822</v>
+      </c>
+      <c r="Y19">
+        <v>0.263135272</v>
+      </c>
+      <c r="Z19">
+        <v>0.3691635368906328</v>
+      </c>
+      <c r="AA19">
+        <v>2.105725</v>
+      </c>
+      <c r="AB19">
+        <v>0.175599191050468</v>
+      </c>
+      <c r="AC19">
+        <v>40.43936595360418</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.62277763889</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>230.7525849643119</v>
       </c>
-      <c r="V20">
-        <v>0.6036863278420316</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.25892796</v>
+      </c>
+      <c r="Y20">
+        <v>0.263138456</v>
+      </c>
+      <c r="Z20">
+        <v>0.3691687087170655</v>
+      </c>
+      <c r="AA20">
+        <v>2.105248000000003</v>
+      </c>
+      <c r="AB20">
+        <v>0.1756413013580023</v>
+      </c>
+      <c r="AC20">
+        <v>40.52968431485474</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.62289395833</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>230.9041563467687</v>
       </c>
-      <c r="V21">
-        <v>0.3179276047549705</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.258948006</v>
+      </c>
+      <c r="Y21">
+        <v>0.263148326</v>
+      </c>
+      <c r="Z21">
+        <v>0.3691898038786802</v>
+      </c>
+      <c r="AA21">
+        <v>2.100159999999995</v>
+      </c>
+      <c r="AB21">
+        <v>0.1760754733868563</v>
+      </c>
+      <c r="AC21">
+        <v>40.65655863574997</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.62300969908</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>230.1806580100056</v>
       </c>
-      <c r="V22">
-        <v>0.38155911912873</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.25895787</v>
+      </c>
+      <c r="Y22">
+        <v>0.263147052</v>
+      </c>
+      <c r="Z22">
+        <v>0.3691958144551852</v>
+      </c>
+      <c r="AA22">
+        <v>2.094591000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.1765449715225068</v>
+      </c>
+      <c r="AC22">
+        <v>40.63723771340832</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.62312601852</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>229.7064723255076</v>
       </c>
-      <c r="V23">
-        <v>0.6031512968660332</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.258960416</v>
+      </c>
+      <c r="Y23">
+        <v>0.263150554</v>
+      </c>
+      <c r="Z23">
+        <v>0.3692000963236601</v>
+      </c>
+      <c r="AA23">
+        <v>2.095069000000002</v>
+      </c>
+      <c r="AB23">
+        <v>0.1765068616931262</v>
+      </c>
+      <c r="AC23">
+        <v>40.5447685407743</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.62324175926</v>
       </c>
@@ -2121,11 +2502,26 @@
       <c r="U24">
         <v>229.6738426046293</v>
       </c>
-      <c r="V24">
-        <v>0.2836601890748635</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.258965824</v>
+      </c>
+      <c r="Y24">
+        <v>0.263157878</v>
+      </c>
+      <c r="Z24">
+        <v>0.3692091097920823</v>
+      </c>
+      <c r="AA24">
+        <v>2.096026999999999</v>
+      </c>
+      <c r="AB24">
+        <v>0.1764307406715723</v>
+      </c>
+      <c r="AC24">
+        <v>40.52152616362086</v>
       </c>
     </row>
   </sheetData>
